--- a/important_mails_2026-05-26.xlsx
+++ b/important_mails_2026-05-26.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,146 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 20 May 2026 02:44:04 +0000</t>
+          <t>Tue, 26 May 2026 12:22:30 +0000 (UTC)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>TikTok Shop &lt;tiktokshopseller@shop.tiktok.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (y8kVKdPDvp)</t>
+          <t>借助这些高潜力商品加速你的业务成长</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ 借助这些高潜力商品加速你的业务成长
+ ToyPuzzle
+ ToyPuzzle，已有超 5 万名商家在使用“商品机会”提升销量。过去 30 天，你错失了一批热销商品，它们的销售潜力约为 TikTok Shop 其他商品的 3 倍（基于过去 30 天的销售数据）。我们为你精心定制了一份个性化商品清单，助你开启销售新机遇。
+ 为何要使用“商品机会”
+ 发现顾客正在主动搜索的热门商品。
+ 上架火爆热卖商品，助力你脱颖而出，增加曝光机会。
+ 解锁专属支持权益，帮助你更快打造热销商品。
+ 表现
+ 查看头部 10% 商家的表现，排名依据为“过去 30 天内通过‘商品机会’产生的销售额占总销售额的百分比”。
+ 月度平均指标
+ 发品总数
+ 613
+ 动销发品数
+ 327
+ 下单数
+ 20310
+ 店铺 GMV 贡献占比
+ 84.96
+ 为你推荐
+ 我们根据你的店铺类目，筛选了热门商品，助你快速提升销量。
+ 操作
+ 类型
+ 图片
+ 商品
+ 类目
+ 销量（过去 30 天）
+ 可上架商品数
+ 添加商品
+ 关键词
+ gray stripe
+ Stuffed Toys
+ /
+ 0
+ 添加商品
+ 关键词
+ plushie army
+ Stuffed Toys
+ /
+ 27
+ 添加商品
+ 关键词
+ action figures
+ Action &amp; Toy Figures
+ /
+ 883
+ 添加商品
+ 关键词
+ tmnt fugglers
+ Stuffed Toys
+ /
+ 209
+ 添加商品
+ 关键词
+ action figure
+ Action &amp; Toy Figures
+ /
+ 493
+ 添加商品
+ 关键词
+ halloween collection
+ Stuffed Toys
+ /
+ 24
+ 添加商品
+ 关键词
+ cute capybara plush
+ Stuffed Toys
+ /
+ 150
+ 添加商品
+ 关键词
+ cookie lover
+ Stuffed Toys
+ /
+ 24
+ 查看更多
+ 热销商品
+ 根据过去 30 天的销售数据，这些商品的成交概率是普通商品的 3 倍。
+ 操作
+ 图片
+ 商品
+ 类目
+ 添加商品
+ 4E&amp;#39;s Novelty Inflatable Limbo Game for Kids Adults 62&amp;#34; Luau Party Game, Indoor Outdoor Inflatable Lawn Yard Games, Summer Hawaiian Birthday Activity Carnival Game
+ Floor Games
+ 添加商品
+ Think Academy Learning Pad - Screen Free Tablet with Flash Cards Inserted to Learn Alph</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 02:44:04 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (y8kVKdPDvp)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -534,39 +659,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 14:39:47 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -586,39 +711,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -638,39 +763,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -687,39 +812,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -739,39 +864,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -791,59 +916,10 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 19 May 2026 15:21:19 +0000</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>View your China tax report for January - March 2026</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96
- We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
- Hello,
-According to new rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
-We’ve submitted your quarterly tax report covering January to March 2026, which includes your identity information, number of transactions, revenue, and commission and service fees.
- Download your quarterly report (link active for seven days)
-This report is provided for your reference only, no action is required.
-Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
- Download your order-level report (link active for seven days)
- Considering that the links are only valid for 7 days, we will resend the email to you again.
-Note : Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
-We’ll continue to provide you with quarterly updates on data share</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -858,235 +934,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 15:07:05 +0000</t>
+          <t>Mon, 25 May 2026 03:58:41 +0000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+          <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>View your China tax report for January-March 2026</t>
+          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
+ DOC REVIEW</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>96
- We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
- Hello,
-According to new rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
-We’ve submitted your quarterly tax report covering January to March 2026, which includes your identity information, number of transactions, revenue, and commission and service fees.
- Download your quarterly report (link active for seven days)
-This report is provided for your reference only – no action is required.
-Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
- Download your order-level report (link active for seven days)
- Considering that the links are only valid for 7 days, we will resend the email to you again.
-Note : Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
-We’ll continue to provide you with quarterly updates on data shar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 19 May 2026 14:48:57 +0000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 05/19/26 14:48 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 412.05.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 19 May 2026 11:16:42 +0000</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>✅ Transparency Payment Confirmed!</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello,
-Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
-Invoice Number: 1N3K-GFF4-JYTJ...
-Hello,
-Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
-Invoice Number: 1N3K-GFF4-JYTJ
-Date: May 19, 2026
-Amount Paid: 572.90 USD
-Remaining Balance: 0.00 USD
-Payment Method: Cash Transfer
-You can access all your billing and payments related information by going to your Transactions Dashboard.
- [Link to invoice Dashboard]
- If you see an 'Access Denied' error message when you use the link below and are not able to access the invoice/credit note, then please email transparency-support@amazon.com with your profile link (see instructions below).
- Frequently Asked Questions (FAQ)
- I see 'Access Denied' message after logging into the Transparency Portal, what should I do?
-- Please log into your Amazon.com account associated with this email address. If you don't have an account, please create one with this email address.
-- Go to https://www.amazon.com/profile.
-- Copy the URL that was generated in the search bar. The profile link you need to provide will look similar to this: https://www.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 19 May 2026 11:16:19 +0000</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>✅ Transparency Payment Confirmed!</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello,
-Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
-Invoice Number: 137D-GY9D-LNDM...
-Hello,
-Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
-Invoice Number: 137D-GY9D-LNDM
-Date: May 19, 2026
-Amount Paid: 751.75 USD
-Remaining Balance: 0.00 USD
-Payment Method: Cash Transfer
-You can access all your billing and payments related information by going to your Transactions Dashboard.
- [Link to invoice Dashboard]
- If you see an 'Access Denied' error message when you use the link below and are not able to access the invoice/credit note, then please email transparency-support@amazon.com with your profile link (see instructions below).
- Frequently Asked Questions (FAQ)
- I see 'Access Denied' message after logging into the Transparency Portal, what should I do?
-- Please log into your Amazon.com account associated with this email address. If you don't have an account, please create one with this email address.
-- Go to https://www.amazon.com/profile.
-- Copy the URL that was generated in the search bar. The profile link you need to provide will look similar to this: https://www.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 25 May 2026 03:58:41 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
- DOC REVIEW</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -1103,40 +966,40 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:53:39 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -1153,40 +1016,40 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:49:38 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC - DOC REVIEW
@@ -1203,39 +1066,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:02:52 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -1255,40 +1118,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:57:24 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -1304,40 +1167,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:55:04 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.fr" &lt;cscompliance-docreview-seller@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review
@@ -1353,39 +1216,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1404,39 +1267,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 17:10:44 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1454,39 +1317,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 08:12:17 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Il team di Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Nuova convalida dei numeri di spedizione attiva da oggi</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorniamo i parametri di convalida dei numeri di spedizione per le spedizioni con corrieri non affiliati, includendo controlli relativi alla lunghezza, al formato previsto del corriere e ai requisiti aggiuntivi relativi ai caratteri. Questo ci permetterà di elaborare il tuo inventario più velocemente.
@@ -1497,39 +1360,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 07:52:06 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Disponible desde hoy la nueva validación del número de seguimiento</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Hemos añadido parámetros de validación del número de seguimiento en los envíos con transportistas no asociados para comprobar la longitud, formato previsto del transportista y requisitos de caracteres adicionales y así procesar tu inventario más rápido.
@@ -1541,39 +1404,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1589,39 +1452,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 08:56:06 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>5月27日前入库助力Prime Day成功</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -1651,39 +1514,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1698,39 +1561,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1745,39 +1608,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1792,39 +1655,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1839,39 +1702,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1886,39 +1749,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1936,88 +1799,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 19 May 2026 15:55:42 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
-Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
-Dear Selling Partner,
-Great news! For a limited time, we're supercharging our Customs Clearance and Shipping Services (C2S2) sign-up offer to help you move your inventory between the UK and EU. Getting set up with C2S2 now helps you stay ahead of upcoming EU customs reforms that will introduce new duties and fees on cross-border shipments. C2S2's per-shipment pricing model helps you manage these rising costs and with this limited-time offer, you'll also save on your first 3 shipments.
-Your Enhanced Sign-Up Offer
-From May 1 to July 31, 2026, eligible sellers who have not yet shipped with C2S2 can receive:
-- 3 FREE shipment brokerage fees (triple the standard offer)
-- 1st year Indirect Representation (IR) FREE (€200 value)
-That's up to €380 in savings on shipping with AVASK or €740 in savings on shipping with RXO, supporting both Small Parcel Delivery (SPD) and Less than Truckload (LTL) pallet solutions.
-How to Get Started
-- New to Amazon Cross-Border Shipping?
-Sign up now and claim your 3 FREE br</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2040,39 +1854,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2096,40 +1910,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -2145,39 +1959,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -2193,39 +2007,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2251,39 +2065,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2299,39 +2113,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2356,39 +2170,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2408,39 +2222,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2460,39 +2274,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2512,39 +2326,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2565,39 +2379,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2617,39 +2431,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2669,39 +2483,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -2717,39 +2531,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2769,6 +2583,268 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 15:21:19 +0000</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>View your China tax report for January - March 2026</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>96
+ We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
+ Hello,
+According to new rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
+We’ve submitted your quarterly tax report covering January to March 2026, which includes your identity information, number of transactions, revenue, and commission and service fees.
+ Download your quarterly report (link active for seven days)
+This report is provided for your reference only, no action is required.
+Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
+ Download your order-level report (link active for seven days)
+ Considering that the links are only valid for 7 days, we will resend the email to you again.
+Note : Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
+We’ll continue to provide you with quarterly updates on data share</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 15:07:05 +0000</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>View your China tax report for January-March 2026</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>96
+ We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
+ Hello,
+According to new rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
+We’ve submitted your quarterly tax report covering January to March 2026, which includes your identity information, number of transactions, revenue, and commission and service fees.
+ Download your quarterly report (link active for seven days)
+This report is provided for your reference only – no action is required.
+Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
+ Download your order-level report (link active for seven days)
+ Considering that the links are only valid for 7 days, we will resend the email to you again.
+Note : Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
+We’ll continue to provide you with quarterly updates on data shar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 14:48:57 +0000</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 05/19/26 14:48 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 412.05.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 11:16:42 +0000</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>✅ Transparency Payment Confirmed!</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello,
+Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
+Invoice Number: 1N3K-GFF4-JYTJ...
+Hello,
+Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
+Invoice Number: 1N3K-GFF4-JYTJ
+Date: May 19, 2026
+Amount Paid: 572.90 USD
+Remaining Balance: 0.00 USD
+Payment Method: Cash Transfer
+You can access all your billing and payments related information by going to your Transactions Dashboard.
+ [Link to invoice Dashboard]
+ If you see an 'Access Denied' error message when you use the link below and are not able to access the invoice/credit note, then please email transparency-support@amazon.com with your profile link (see instructions below).
+ Frequently Asked Questions (FAQ)
+ I see 'Access Denied' message after logging into the Transparency Portal, what should I do?
+- Please log into your Amazon.com account associated with this email address. If you don't have an account, please create one with this email address.
+- Go to https://www.amazon.com/profile.
+- Copy the URL that was generated in the search bar. The profile link you need to provide will look similar to this: https://www.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 11:16:19 +0000</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>✅ Transparency Payment Confirmed!</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello,
+Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
+Invoice Number: 137D-GY9D-LNDM...
+Hello,
+Thank you for your purchase! Your payment has been successfully processed. Here is your payment summary:
+Invoice Number: 137D-GY9D-LNDM
+Date: May 19, 2026
+Amount Paid: 751.75 USD
+Remaining Balance: 0.00 USD
+Payment Method: Cash Transfer
+You can access all your billing and payments related information by going to your Transactions Dashboard.
+ [Link to invoice Dashboard]
+ If you see an 'Access Denied' error message when you use the link below and are not able to access the invoice/credit note, then please email transparency-support@amazon.com with your profile link (see instructions below).
+ Frequently Asked Questions (FAQ)
+ I see 'Access Denied' message after logging into the Transparency Portal, what should I do?
+- Please log into your Amazon.com account associated with this email address. If you don't have an account, please create one with this email address.
+- Go to https://www.amazon.com/profile.
+- Copy the URL that was generated in the search bar. The profile link you need to provide will look similar to this: https://www.</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
@@ -3732,7 +3808,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3747,123 +3823,22 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
+          <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Tu pago está en camino</t>
+          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
+ - DOC REVIEW</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 04/26/26 14:08 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 221,28.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 04/26/26 14:08 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 224.28.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 18 May 2026 07:24:17 +0000</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
- - DOC REVIEW</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3879,40 +3854,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3926,40 +3901,40 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3973,40 +3948,40 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -4019,39 +3994,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4071,39 +4046,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -4128,39 +4103,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -4185,40 +4160,40 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4233,40 +4208,40 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4280,40 +4255,40 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4327,41 +4302,41 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -4372,39 +4347,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4423,39 +4398,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4479,39 +4454,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4529,39 +4504,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4579,39 +4554,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4629,39 +4604,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4679,39 +4654,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4729,39 +4704,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4777,39 +4752,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4827,39 +4802,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4877,39 +4852,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4919,39 +4894,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4972,39 +4947,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -5020,39 +4995,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -5071,39 +5046,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -5114,39 +5089,88 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 15:55:42 +0000</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
+Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
+Dear Selling Partner,
+Great news! For a limited time, we're supercharging our Customs Clearance and Shipping Services (C2S2) sign-up offer to help you move your inventory between the UK and EU. Getting set up with C2S2 now helps you stay ahead of upcoming EU customs reforms that will introduce new duties and fees on cross-border shipments. C2S2's per-shipment pricing model helps you manage these rising costs and with this limited-time offer, you'll also save on your first 3 shipments.
+Your Enhanced Sign-Up Offer
+From May 1 to July 31, 2026, eligible sellers who have not yet shipped with C2S2 can receive:
+- 3 FREE shipment brokerage fees (triple the standard offer)
+- 1st year Indirect Representation (IR) FREE (€200 value)
+That's up to €380 in savings on shipping with AVASK or €740 in savings on shipping with RXO, supporting both Small Parcel Delivery (SPD) and Less than Truckload (LTL) pallet solutions.
+How to Get Started
+- New to Amazon Cross-Border Shipping?
+Sign up now and claim your 3 FREE br</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5165,39 +5189,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5212,40 +5236,40 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5261,39 +5285,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -5309,39 +5333,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -5362,39 +5386,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5409,39 +5433,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -5471,39 +5495,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5531,39 +5555,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -5579,39 +5603,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5630,39 +5654,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -5684,39 +5708,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5738,39 +5762,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -5789,39 +5813,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5833,39 +5857,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5877,39 +5901,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -5921,39 +5945,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5965,39 +5989,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6009,39 +6033,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6053,39 +6077,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6104,39 +6128,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6155,39 +6179,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -6199,39 +6223,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6243,39 +6267,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6287,39 +6311,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6331,39 +6355,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -6375,39 +6399,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6419,39 +6443,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6463,39 +6487,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6507,39 +6531,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6551,39 +6575,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6595,39 +6619,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6639,39 +6663,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6683,39 +6707,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6727,40 +6751,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6779,39 +6803,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6823,39 +6847,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6867,39 +6891,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6911,39 +6935,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6955,39 +6979,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6999,39 +7023,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7052,39 +7076,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7099,39 +7123,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -7150,39 +7174,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7204,39 +7228,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -7262,40 +7286,40 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7311,40 +7335,40 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7360,39 +7384,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7408,39 +7432,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7456,39 +7480,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7504,39 +7528,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7550,39 +7574,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -7600,40 +7624,40 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7649,39 +7673,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7697,39 +7721,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7745,40 +7769,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7794,39 +7818,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7843,39 +7867,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -7904,39 +7928,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7952,39 +7976,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7998,39 +8022,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8045,39 +8069,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8097,39 +8121,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -8158,40 +8182,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -8204,39 +8228,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -8251,39 +8275,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -8296,40 +8320,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -8344,40 +8368,40 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -8391,39 +8415,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -8437,39 +8461,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -8484,39 +8508,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -8530,39 +8554,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -8577,39 +8601,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8624,39 +8648,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8675,87 +8699,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>¡Buenos días!
-Espero que te encuentres bien.
-Mi nombre es Gabriel Martins y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
-Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
-Sobre Worten.
-Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
-En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
-Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
-Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
-Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
-Worten Marketplace tiene una estrategia B2C,</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8779,39 +8755,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8832,39 +8808,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8887,39 +8863,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8943,39 +8919,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8998,39 +8974,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9054,39 +9030,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -9095,39 +9071,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9157,39 +9133,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除

--- a/important_mails_2026-05-26.xlsx
+++ b/important_mails_2026-05-26.xlsx
@@ -1219,7 +1219,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1234,72 +1234,21 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tue, 19 May 2026 17:11:27 +0000</t>
+          <t>Mon, 25 May 2026 17:10:44 +0000</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
+          <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 06/17/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FCDRNTT8
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-474991238288257</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 25 May 2026 17:10:44 +0000</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1317,39 +1266,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 08:12:17 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Il team di Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Nuova convalida dei numeri di spedizione attiva da oggi</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorniamo i parametri di convalida dei numeri di spedizione per le spedizioni con corrieri non affiliati, includendo controlli relativi alla lunghezza, al formato previsto del corriere e ai requisiti aggiuntivi relativi ai caratteri. Questo ci permetterà di elaborare il tuo inventario più velocemente.
@@ -1360,39 +1309,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 07:52:06 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Disponible desde hoy la nueva validación del número de seguimiento</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Hemos añadido parámetros de validación del número de seguimiento en los envíos con transportistas no asociados para comprobar la longitud, formato previsto del transportista y requisitos de caracteres adicionales y así procesar tu inventario más rápido.
@@ -1404,39 +1353,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1452,39 +1401,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 08:56:06 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>5月27日前入库助力Prime Day成功</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -1514,39 +1463,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1561,39 +1510,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1608,39 +1557,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -1655,39 +1604,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1702,39 +1651,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1749,89 +1698,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 19 May 2026 17:10:53 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Hola Weihai EU,
-Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
-Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
-¿Estaría disponible para una reunión online esta semana?
-Acerca de Worten - Somos el líder del mercado portugués:
-- Nº 1 del comercio electrónico portugués
-- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
-- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
-- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
-- Sin costes iniciales - 6 meses
-Estaré encantado de ayudarle si tiene alguna pregunta.
-Muchas gracias,
-Saludos Cordiales</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1854,39 +1753,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1910,40 +1809,40 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1959,39 +1858,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -2007,39 +1906,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2065,39 +1964,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2113,39 +2012,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2170,39 +2069,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2222,39 +2121,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2274,39 +2173,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2326,39 +2225,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2379,39 +2278,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2431,39 +2330,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2483,39 +2382,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -2531,39 +2430,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2583,39 +2482,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2632,39 +2531,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2681,39 +2580,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2733,39 +2632,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -2789,39 +2688,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -2845,39 +2744,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2897,39 +2796,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2949,39 +2848,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3001,39 +2900,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3053,39 +2952,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3101,39 +3000,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3150,39 +3049,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3202,39 +3101,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -3251,39 +3150,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3300,39 +3199,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3352,39 +3251,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3404,39 +3303,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3453,39 +3352,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3500,39 +3399,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3548,39 +3447,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3600,39 +3499,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3652,39 +3551,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3701,39 +3600,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3753,39 +3652,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3805,40 +3704,91 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 17:11:27 +0000</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 06/17/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FCDRNTT8
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-474991238288257</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3854,40 +3804,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3901,40 +3851,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3948,40 +3898,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -3994,39 +3944,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4046,39 +3996,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -4103,39 +4053,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -4160,40 +4110,40 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4208,40 +4158,40 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4255,40 +4205,40 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4302,41 +4252,41 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -4347,39 +4297,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4398,39 +4348,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4454,39 +4404,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4504,39 +4454,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4554,39 +4504,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4604,39 +4554,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4654,39 +4604,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4704,39 +4654,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4752,39 +4702,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4802,39 +4752,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4852,39 +4802,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4894,39 +4844,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4947,39 +4897,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4995,39 +4945,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -5046,39 +4996,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -5086,6 +5036,56 @@
 You submission to address the Regulatory Compliance was rejected. This request applies to you if you are fulfilling your chemical products via the Amazon Fulfillment Network (AFN) and this compliance request is for a Safety Data Sheet (SDS). If you are using another method of fulfillment, such as the Merchant Fulfillment Network (MFN), please disregard this request.
 Chemical Safety and Compliance (CSC) classifies Hazardous Goods (HG), which are a category of chemical products. These chemical products are regulated for storage, handling and waste by country or region level legislation, as they pose a risk to property, human health or the environment if spilled or released.
 To mitigate this risk, CSC requires the submission of Safety Data Sheets (SDS), based on the Toxic Substances Control Act (TSCA) and Occupation</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 17:10:53 +0000</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Hola Weihai EU,
+Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
+¿Estaría disponible para una reunión online esta semana?
+Acerca de Worten - Somos el líder del mercado portugués:
+- Nº 1 del comercio electrónico portugués
+- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes iniciales - 6 meses
+Estaré encantado de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos Cordiales</t>
         </is>
       </c>
     </row>
